--- a/owlcms/src/main/resources/templates/records/prettyGroups.xlsx
+++ b/owlcms/src/main/resources/templates/records/prettyGroups.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lamyj\git\owlcms4\owlcms\src\main\resources\templates\records\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\git\owlcms_v23\owlcms\src\main\resources\templates\records\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11422B7A-DF68-4F36-B9B6-9D60361FFF53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C440CB20-3C0F-4E34-92FB-10556CD9674E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
             <family val="2"/>
           </rPr>
           <t>jx:area(lastCell="P4")
-jx:each(items="agegroups" var="ag" lastCell="P4")</t>
+jx:each(items="agegroups" var="ag" lastCell="L4")</t>
         </r>
       </text>
     </comment>
@@ -57,7 +57,7 @@
             <rFont val="Tahoma"/>
             <charset val="1"/>
           </rPr>
-          <t>jx:each(items="ag.value" var="r" lastCell="P3")</t>
+          <t>jx:each(items="ag.value" var="r" lastCell="L3")</t>
         </r>
       </text>
     </comment>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>${r.recordFederation}</t>
   </si>
@@ -77,24 +77,12 @@
     <t>${r.ageGrp}</t>
   </si>
   <si>
-    <t>${r.ageGrpLower}</t>
-  </si>
-  <si>
-    <t>${r.ageGrpUpper}</t>
-  </si>
-  <si>
-    <t>${r.bwCatLower}</t>
-  </si>
-  <si>
     <t>${r.recordValue}</t>
   </si>
   <si>
     <t>${r.athleteName}</t>
   </si>
   <si>
-    <t>${r.birth}</t>
-  </si>
-  <si>
     <t>${r.nation}</t>
   </si>
   <si>
@@ -116,15 +104,6 @@
     <t>${t.get("Records."+"AgeGroup")}</t>
   </si>
   <si>
-    <t>${t.get("Records."+"ageLow")}</t>
-  </si>
-  <si>
-    <t>${t.get("Records."+"ageUpper")}</t>
-  </si>
-  <si>
-    <t>${t.get("Records."+"bwLow")}</t>
-  </si>
-  <si>
     <t>${t.get("Records."+"Lift")}</t>
   </si>
   <si>
@@ -132,9 +111,6 @@
   </si>
   <si>
     <t>${t.get("Records."+"Name")}</t>
-  </si>
-  <si>
-    <t>${t.get("Records."+"Born")}</t>
   </si>
   <si>
     <t>${t.get("Records."+"Nation")}</t>
@@ -246,7 +222,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -266,15 +242,6 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -297,9 +264,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -629,100 +593,82 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R30"/>
+  <dimension ref="A1:N30"/>
   <sheetFormatPr defaultColWidth="15.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="15.7109375" style="3"/>
-    <col min="5" max="7" width="0" style="8" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="15.7109375" style="13"/>
+    <col min="5" max="5" width="15.7109375" style="10"/>
+    <col min="6" max="6" width="15.7109375" style="3"/>
+    <col min="7" max="7" width="15.7109375" style="10"/>
+    <col min="8" max="8" width="30.28515625" style="3" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="3"/>
-    <col min="10" max="10" width="15.7109375" style="13"/>
-    <col min="11" max="11" width="30.28515625" style="3" customWidth="1"/>
-    <col min="12" max="12" width="0" style="6" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="15.7109375" style="3"/>
-    <col min="14" max="14" width="15.7109375" style="6"/>
-    <col min="15" max="16" width="15.7109375" style="3"/>
-    <col min="17" max="17" width="0" style="3" hidden="1" customWidth="1"/>
-    <col min="18" max="16384" width="15.7109375" style="3"/>
+    <col min="10" max="10" width="15.7109375" style="6"/>
+    <col min="11" max="12" width="15.7109375" style="3"/>
+    <col min="13" max="13" width="0" style="3" hidden="1" customWidth="1"/>
+    <col min="14" max="16384" width="15.7109375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="22" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="20"/>
-      <c r="O1" s="21"/>
-      <c r="P1" s="21"/>
-      <c r="Q1" s="19"/>
-      <c r="R1" s="19"/>
-    </row>
-    <row r="2" spans="1:18" s="13" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="14" t="s">
+    <row r="1" spans="1:14" s="18" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
+    </row>
+    <row r="2" spans="1:14" s="10" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="H2" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="I2" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="E2" s="9" t="s">
+      <c r="J2" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="K2" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="L2" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="M2" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="H2" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="I2" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="J2" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="K2" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="L2" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="M2" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="N2" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="O2" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="P2" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q2" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="R2" s="10"/>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="N2" s="7"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
@@ -733,500 +679,380 @@
         <v>2</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E3" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="H3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="I3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="J3" s="11" t="s">
+      <c r="J3" s="5" t="s">
         <v>6</v>
       </c>
       <c r="K3" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="M3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="L3" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="N3" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="O3" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="P3" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q3" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="R3" s="4"/>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="N3" s="4"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="11"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="1"/>
       <c r="I4" s="1"/>
-      <c r="J4" s="12"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="2"/>
-      <c r="O4" s="4"/>
-      <c r="P4" s="4"/>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="J4" s="2"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="11"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="1"/>
       <c r="I5" s="1"/>
-      <c r="J5" s="12"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="2"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="2"/>
-      <c r="O5" s="4"/>
-      <c r="P5" s="4"/>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="J5" s="2"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="11"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="1"/>
       <c r="I6" s="1"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="2"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="2"/>
-      <c r="O6" s="4"/>
-      <c r="P6" s="4"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="J6" s="2"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="11"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="1"/>
       <c r="I8" s="1"/>
-      <c r="J8" s="12"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="1"/>
-      <c r="N8" s="2"/>
-      <c r="O8" s="4"/>
-      <c r="P8" s="4"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="J8" s="2"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="11"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="1"/>
       <c r="I9" s="1"/>
-      <c r="J9" s="12"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="2"/>
-      <c r="M9" s="1"/>
-      <c r="N9" s="2"/>
-      <c r="O9" s="4"/>
-      <c r="P9" s="4"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="J9" s="2"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="11"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="1"/>
       <c r="I10" s="1"/>
-      <c r="J10" s="12"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="1"/>
-      <c r="N10" s="2"/>
-      <c r="O10" s="4"/>
-      <c r="P10" s="4"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="J10" s="2"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="11"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="1"/>
       <c r="I11" s="1"/>
-      <c r="J11" s="12"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="2"/>
-      <c r="M11" s="1"/>
-      <c r="N11" s="2"/>
-      <c r="O11" s="4"/>
-      <c r="P11" s="4"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="J11" s="2"/>
+      <c r="K11" s="4"/>
+      <c r="L11" s="4"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="11"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="1"/>
       <c r="I12" s="1"/>
-      <c r="J12" s="12"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="2"/>
-      <c r="M12" s="1"/>
-      <c r="N12" s="2"/>
-      <c r="O12" s="4"/>
-      <c r="P12" s="4"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="J12" s="2"/>
+      <c r="K12" s="4"/>
+      <c r="L12" s="4"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="11"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="1"/>
       <c r="I13" s="1"/>
-      <c r="J13" s="12"/>
-      <c r="K13" s="1"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="1"/>
-      <c r="N13" s="2"/>
-      <c r="O13" s="4"/>
-      <c r="P13" s="4"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="J13" s="2"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="11"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="1"/>
       <c r="I14" s="1"/>
-      <c r="J14" s="12"/>
-      <c r="K14" s="1"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="1"/>
-      <c r="N14" s="2"/>
-      <c r="O14" s="4"/>
-      <c r="P14" s="4"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="J14" s="2"/>
+      <c r="K14" s="4"/>
+      <c r="L14" s="4"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="11"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="1"/>
       <c r="I15" s="1"/>
-      <c r="J15" s="12"/>
-      <c r="K15" s="1"/>
-      <c r="L15" s="2"/>
-      <c r="M15" s="1"/>
-      <c r="N15" s="2"/>
-      <c r="O15" s="4"/>
-      <c r="P15" s="4"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="J15" s="2"/>
+      <c r="K15" s="4"/>
+      <c r="L15" s="4"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="11"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="1"/>
       <c r="I16" s="1"/>
-      <c r="J16" s="12"/>
-      <c r="K16" s="1"/>
-      <c r="L16" s="2"/>
-      <c r="M16" s="1"/>
-      <c r="N16" s="2"/>
-      <c r="O16" s="4"/>
-      <c r="P16" s="4"/>
-    </row>
-    <row r="17" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="J16" s="2"/>
+      <c r="K16" s="4"/>
+      <c r="L16" s="4"/>
+    </row>
+    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="11"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="1"/>
       <c r="I17" s="1"/>
-      <c r="J17" s="12"/>
-      <c r="K17" s="1"/>
-      <c r="L17" s="2"/>
-      <c r="M17" s="1"/>
-      <c r="N17" s="2"/>
-      <c r="O17" s="4"/>
-      <c r="P17" s="4"/>
-    </row>
-    <row r="18" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="J17" s="2"/>
+      <c r="K17" s="4"/>
+      <c r="L17" s="4"/>
+    </row>
+    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="11"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="1"/>
       <c r="I18" s="1"/>
-      <c r="J18" s="12"/>
-      <c r="K18" s="1"/>
-      <c r="L18" s="2"/>
-      <c r="M18" s="1"/>
-      <c r="N18" s="2"/>
-      <c r="O18" s="4"/>
-      <c r="P18" s="4"/>
-    </row>
-    <row r="19" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="J18" s="2"/>
+      <c r="K18" s="4"/>
+      <c r="L18" s="4"/>
+    </row>
+    <row r="19" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="11"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="1"/>
       <c r="I19" s="1"/>
-      <c r="J19" s="12"/>
-      <c r="K19" s="1"/>
-      <c r="L19" s="2"/>
-      <c r="M19" s="1"/>
-      <c r="N19" s="2"/>
-      <c r="O19" s="4"/>
-      <c r="P19" s="4"/>
-    </row>
-    <row r="20" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="J19" s="2"/>
+      <c r="K19" s="4"/>
+      <c r="L19" s="4"/>
+    </row>
+    <row r="20" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
       <c r="D20" s="4"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="11"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="1"/>
       <c r="I20" s="1"/>
-      <c r="J20" s="12"/>
-      <c r="K20" s="1"/>
-      <c r="L20" s="2"/>
-      <c r="M20" s="1"/>
-      <c r="N20" s="2"/>
-      <c r="O20" s="4"/>
-      <c r="P20" s="4"/>
-    </row>
-    <row r="21" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="J20" s="2"/>
+      <c r="K20" s="4"/>
+      <c r="L20" s="4"/>
+    </row>
+    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="11"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="9"/>
+      <c r="H21" s="1"/>
       <c r="I21" s="1"/>
-      <c r="J21" s="12"/>
-      <c r="K21" s="1"/>
-      <c r="L21" s="2"/>
-      <c r="M21" s="1"/>
-      <c r="N21" s="2"/>
-      <c r="O21" s="4"/>
-      <c r="P21" s="4"/>
-    </row>
-    <row r="22" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="J21" s="2"/>
+      <c r="K21" s="4"/>
+      <c r="L21" s="4"/>
+    </row>
+    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
       <c r="D22" s="4"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="11"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="9"/>
+      <c r="H22" s="1"/>
       <c r="I22" s="1"/>
-      <c r="J22" s="12"/>
-      <c r="K22" s="1"/>
-      <c r="L22" s="2"/>
-      <c r="M22" s="1"/>
-      <c r="N22" s="2"/>
-      <c r="O22" s="4"/>
-      <c r="P22" s="4"/>
-    </row>
-    <row r="23" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="J22" s="2"/>
+      <c r="K22" s="4"/>
+      <c r="L22" s="4"/>
+    </row>
+    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
-      <c r="G23" s="7"/>
-      <c r="H23" s="11"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="9"/>
+      <c r="H23" s="1"/>
       <c r="I23" s="1"/>
-      <c r="J23" s="12"/>
-      <c r="K23" s="1"/>
-      <c r="L23" s="2"/>
-      <c r="M23" s="1"/>
-      <c r="N23" s="2"/>
-      <c r="O23" s="4"/>
-      <c r="P23" s="4"/>
-    </row>
-    <row r="24" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="J23" s="2"/>
+      <c r="K23" s="4"/>
+      <c r="L23" s="4"/>
+    </row>
+    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
       <c r="D24" s="4"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="11"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="9"/>
+      <c r="H24" s="1"/>
       <c r="I24" s="1"/>
-      <c r="J24" s="12"/>
-      <c r="K24" s="1"/>
-      <c r="L24" s="2"/>
-      <c r="M24" s="1"/>
-      <c r="N24" s="2"/>
-      <c r="O24" s="4"/>
-      <c r="P24" s="4"/>
-    </row>
-    <row r="25" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="J24" s="2"/>
+      <c r="K24" s="4"/>
+      <c r="L24" s="4"/>
+    </row>
+    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="7"/>
-      <c r="H25" s="11"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="1"/>
       <c r="I25" s="1"/>
-      <c r="J25" s="12"/>
-      <c r="K25" s="1"/>
-      <c r="L25" s="2"/>
-      <c r="M25" s="1"/>
-      <c r="N25" s="2"/>
-      <c r="O25" s="4"/>
-      <c r="P25" s="4"/>
-    </row>
-    <row r="26" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="J25" s="2"/>
+      <c r="K25" s="4"/>
+      <c r="L25" s="4"/>
+    </row>
+    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="7"/>
-      <c r="H26" s="11"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="1"/>
       <c r="I26" s="1"/>
-      <c r="J26" s="12"/>
-      <c r="K26" s="1"/>
-      <c r="L26" s="2"/>
-      <c r="M26" s="1"/>
-      <c r="N26" s="2"/>
-      <c r="O26" s="4"/>
-      <c r="P26" s="4"/>
-    </row>
-    <row r="27" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="J26" s="2"/>
+      <c r="K26" s="4"/>
+      <c r="L26" s="4"/>
+    </row>
+    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
       <c r="D27" s="4"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="7"/>
-      <c r="G27" s="7"/>
-      <c r="H27" s="11"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="1"/>
       <c r="I27" s="1"/>
-      <c r="J27" s="12"/>
-      <c r="K27" s="1"/>
-      <c r="L27" s="2"/>
-      <c r="M27" s="1"/>
-      <c r="N27" s="2"/>
-      <c r="O27" s="4"/>
-      <c r="P27" s="4"/>
-    </row>
-    <row r="28" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="J27" s="2"/>
+      <c r="K27" s="4"/>
+      <c r="L27" s="4"/>
+    </row>
+    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
       <c r="D28" s="4"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
-      <c r="G28" s="7"/>
-      <c r="H28" s="11"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="1"/>
       <c r="I28" s="1"/>
-      <c r="J28" s="12"/>
-      <c r="K28" s="1"/>
-      <c r="L28" s="2"/>
-      <c r="M28" s="1"/>
-      <c r="N28" s="2"/>
-      <c r="O28" s="4"/>
-      <c r="P28" s="4"/>
-    </row>
-    <row r="29" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="J28" s="2"/>
+      <c r="K28" s="4"/>
+      <c r="L28" s="4"/>
+    </row>
+    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="7"/>
-      <c r="G29" s="7"/>
-      <c r="H29" s="11"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="9"/>
+      <c r="H29" s="1"/>
       <c r="I29" s="1"/>
-      <c r="J29" s="12"/>
-      <c r="K29" s="1"/>
-      <c r="L29" s="2"/>
-      <c r="M29" s="1"/>
-      <c r="N29" s="2"/>
-      <c r="O29" s="4"/>
-      <c r="P29" s="4"/>
-    </row>
-    <row r="30" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="J29" s="2"/>
+      <c r="K29" s="4"/>
+      <c r="L29" s="4"/>
+    </row>
+    <row r="30" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
       <c r="D30" s="4"/>
-      <c r="E30" s="7"/>
-      <c r="F30" s="7"/>
-      <c r="G30" s="7"/>
-      <c r="H30" s="11"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="9"/>
+      <c r="H30" s="1"/>
       <c r="I30" s="1"/>
-      <c r="J30" s="12"/>
-      <c r="K30" s="1"/>
-      <c r="L30" s="2"/>
-      <c r="M30" s="1"/>
-      <c r="N30" s="2"/>
-      <c r="O30" s="4"/>
-      <c r="P30" s="4"/>
+      <c r="J30" s="2"/>
+      <c r="K30" s="4"/>
+      <c r="L30" s="4"/>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G8:H1048576 G3:H6" xr:uid="{53FB7450-D8BD-4FB4-A0E8-29CC05EF8875}">
+  <dataValidations count="1">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E8:E1048576 E3:E6" xr:uid="{53FB7450-D8BD-4FB4-A0E8-29CC05EF8875}">
       <formula1>0</formula1>
       <formula2>250</formula2>
-    </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E8:F1048576 E3:F6" xr:uid="{A2E907D7-3179-4C92-B9E8-43D2D96CBEC9}">
-      <formula1>0</formula1>
-      <formula2>120</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
